--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T13:03:58+00:00</t>
+    <t>2025-05-14T14:13:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:13:57+00:00</t>
+    <t>2025-05-20T08:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T08:55:00+00:00</t>
+    <t>2025-05-21T07:47:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:22+00:00</t>
+    <t>2025-05-21T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:53+00:00</t>
+    <t>2025-05-21T07:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:49:53+00:00</t>
+    <t>2025-05-21T07:50:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:50:26+00:00</t>
+    <t>2025-05-21T07:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:51:14+00:00</t>
+    <t>2025-05-21T07:52:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:52:53+00:00</t>
+    <t>2025-05-21T08:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$85</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T08:04:56+00:00</t>
+    <t>2025-05-21T13:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ce profil représente la structure de prise en charge.</t>
+    <t>Ce profil représente le lieu de la prise en charge.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -853,7 +856,7 @@
     <t>Location.name</t>
   </si>
   <si>
-    <t>Name of the location as used by humans</t>
+    <t>Nom de la structure</t>
   </si>
   <si>
     <t>Name of the location as used by humans. Does not need to be unique.</t>
@@ -944,7 +947,7 @@
     <t>Location.type.coding</t>
   </si>
   <si>
-    <t>Structure de prise en charge : healthCareFacility</t>
+    <t>Code defined by a terminology system</t>
   </si>
   <si>
     <t>A reference to a code defined by a terminology system.</t>
@@ -966,28 +969,28 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Location.type.coding:code</t>
-  </si>
-  <si>
-    <t>code</t>
+    <t>Location.type.coding:secteurActivite</t>
+  </si>
+  <si>
+    <t>secteurActivite</t>
   </si>
   <si>
     <t>Secteur d'activité</t>
   </si>
   <si>
-    <t>Location.type.coding:code.id</t>
+    <t>Location.type.coding:secteurActivite.id</t>
   </si>
   <si>
     <t>Location.type.coding.id</t>
   </si>
   <si>
-    <t>Location.type.coding:code.extension</t>
+    <t>Location.type.coding:secteurActivite.extension</t>
   </si>
   <si>
     <t>Location.type.coding.extension</t>
   </si>
   <si>
-    <t>Location.type.coding:code.system</t>
+    <t>Location.type.coding:secteurActivite.system</t>
   </si>
   <si>
     <t>Location.type.coding.system</t>
@@ -1011,7 +1014,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Location.type.coding:code.version</t>
+    <t>Location.type.coding:secteurActivite.version</t>
   </si>
   <si>
     <t>Location.type.coding.version</t>
@@ -1032,7 +1035,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Location.type.coding:code.code</t>
+    <t>Location.type.coding:secteurActivite.code</t>
   </si>
   <si>
     <t>Location.type.coding.code</t>
@@ -1056,7 +1059,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Location.type.coding:code.display</t>
+    <t>Location.type.coding:secteurActivite.display</t>
   </si>
   <si>
     <t>Location.type.coding.display</t>
@@ -1077,7 +1080,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Location.type.coding:code.userSelected</t>
+    <t>Location.type.coding:secteurActivite.userSelected</t>
   </si>
   <si>
     <t>Location.type.coding.userSelected</t>
@@ -1105,37 +1108,37 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Location.type.coding:translation</t>
-  </si>
-  <si>
-    <t>translation</t>
+    <t>Location.type.coding:categorieEtablissement</t>
+  </si>
+  <si>
+    <t>categorieEtablissement</t>
   </si>
   <si>
     <t>Catégorie d'établissement</t>
   </si>
   <si>
-    <t>Location.type.coding:translation.id</t>
-  </si>
-  <si>
-    <t>Location.type.coding:translation.extension</t>
-  </si>
-  <si>
-    <t>Location.type.coding:translation.system</t>
-  </si>
-  <si>
-    <t>Location.type.coding:translation.version</t>
-  </si>
-  <si>
-    <t>Location.type.coding:translation.code</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-categorie-etablissement</t>
-  </si>
-  <si>
-    <t>Location.type.coding:translation.display</t>
-  </si>
-  <si>
-    <t>Location.type.coding:translation.userSelected</t>
+    <t>Location.type.coding:categorieEtablissement.id</t>
+  </si>
+  <si>
+    <t>Location.type.coding:categorieEtablissement.extension</t>
+  </si>
+  <si>
+    <t>Location.type.coding:categorieEtablissement.system</t>
+  </si>
+  <si>
+    <t>Location.type.coding:categorieEtablissement.version</t>
+  </si>
+  <si>
+    <t>Location.type.coding:categorieEtablissement.code</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j368-categorie-etablissement-cisis</t>
+  </si>
+  <si>
+    <t>Location.type.coding:categorieEtablissement.display</t>
+  </si>
+  <si>
+    <t>Location.type.coding:categorieEtablissement.userSelected</t>
   </si>
   <si>
     <t>Location.type.text</t>
@@ -1186,7 +1189,7 @@
 </t>
   </si>
   <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
+    <t>Adresse géopostale de la structure</t>
   </si>
   <si>
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
@@ -1653,6 +1656,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1829,9 +1847,9 @@
   <dimension ref="A1:AL85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="37.05859375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.18359375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.84765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.66796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.47265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1984,7 +2002,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2090,7 +2108,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>83</v>
       </c>
@@ -2198,7 +2216,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>91</v>
       </c>
@@ -2304,7 +2322,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>97</v>
       </c>
@@ -2410,7 +2428,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>103</v>
       </c>
@@ -2518,7 +2536,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>114</v>
       </c>
@@ -2626,7 +2644,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>119</v>
       </c>
@@ -2734,7 +2752,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>125</v>
       </c>
@@ -2842,7 +2860,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>131</v>
       </c>
@@ -2950,7 +2968,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>139</v>
       </c>
@@ -3060,7 +3078,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>141</v>
       </c>
@@ -3168,7 +3186,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>150</v>
       </c>
@@ -3276,7 +3294,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>158</v>
       </c>
@@ -3384,7 +3402,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>163</v>
       </c>
@@ -3492,7 +3510,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>172</v>
       </c>
@@ -3600,7 +3618,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>180</v>
       </c>
@@ -3708,7 +3726,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>188</v>
       </c>
@@ -3812,7 +3830,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>192</v>
       </c>
@@ -3920,7 +3938,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>197</v>
       </c>
@@ -4030,7 +4048,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>202</v>
       </c>
@@ -4138,7 +4156,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>209</v>
       </c>
@@ -4244,7 +4262,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>210</v>
       </c>
@@ -4352,7 +4370,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>211</v>
       </c>
@@ -4462,7 +4480,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>221</v>
       </c>
@@ -4570,7 +4588,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>229</v>
       </c>
@@ -4680,7 +4698,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>237</v>
       </c>
@@ -4788,7 +4806,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>244</v>
       </c>
@@ -4894,7 +4912,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>250</v>
       </c>
@@ -5002,7 +5020,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>257</v>
       </c>
@@ -5108,7 +5126,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>264</v>
       </c>
@@ -5214,7 +5232,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>269</v>
       </c>
@@ -5233,7 +5251,7 @@
         <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>75</v>
@@ -5322,7 +5340,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>274</v>
       </c>
@@ -5432,7 +5450,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>279</v>
       </c>
@@ -5540,7 +5558,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>284</v>
       </c>
@@ -5650,7 +5668,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>292</v>
       </c>
@@ -5669,7 +5687,7 @@
         <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>75</v>
@@ -5754,7 +5772,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>297</v>
       </c>
@@ -5860,7 +5878,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>298</v>
       </c>
@@ -5968,7 +5986,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>299</v>
       </c>
@@ -6076,7 +6094,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>307</v>
       </c>
@@ -6188,7 +6206,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>310</v>
       </c>
@@ -6294,7 +6312,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>312</v>
       </c>
@@ -6402,7 +6420,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>314</v>
       </c>
@@ -6512,7 +6530,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>322</v>
       </c>
@@ -6620,7 +6638,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>329</v>
       </c>
@@ -6726,7 +6744,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>337</v>
       </c>
@@ -6834,7 +6852,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>344</v>
       </c>
@@ -6944,7 +6962,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>353</v>
       </c>
@@ -7056,7 +7074,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>356</v>
       </c>
@@ -7162,7 +7180,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>357</v>
       </c>
@@ -7270,7 +7288,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>358</v>
       </c>
@@ -7380,7 +7398,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>359</v>
       </c>
@@ -7488,7 +7506,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>360</v>
       </c>
@@ -7594,7 +7612,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>362</v>
       </c>
@@ -7702,7 +7720,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>363</v>
       </c>
@@ -7812,7 +7830,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>364</v>
       </c>
@@ -7922,7 +7940,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>371</v>
       </c>
@@ -8028,7 +8046,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>377</v>
       </c>
@@ -8047,7 +8065,7 @@
         <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>75</v>
@@ -8138,7 +8156,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>384</v>
       </c>
@@ -8244,7 +8262,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>390</v>
       </c>
@@ -8352,7 +8370,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>396</v>
       </c>
@@ -8458,7 +8476,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>397</v>
       </c>
@@ -8566,7 +8584,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>398</v>
       </c>
@@ -8676,7 +8694,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>403</v>
       </c>
@@ -8782,7 +8800,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>408</v>
       </c>
@@ -8888,7 +8906,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>411</v>
       </c>
@@ -8994,7 +9012,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>414</v>
       </c>
@@ -9104,7 +9122,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>420</v>
       </c>
@@ -9212,7 +9230,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>426</v>
       </c>
@@ -9318,7 +9336,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>427</v>
       </c>
@@ -9426,7 +9444,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>428</v>
       </c>
@@ -9534,7 +9552,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>433</v>
       </c>
@@ -9642,7 +9660,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>439</v>
       </c>
@@ -9750,7 +9768,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>446</v>
       </c>
@@ -9858,7 +9876,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>452</v>
       </c>
@@ -9966,7 +9984,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
         <v>457</v>
       </c>
@@ -10074,7 +10092,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
         <v>462</v>
       </c>
@@ -10180,7 +10198,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>463</v>
       </c>
@@ -10288,7 +10306,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
         <v>464</v>
       </c>
@@ -10398,7 +10416,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
         <v>465</v>
       </c>
@@ -10504,7 +10522,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
         <v>470</v>
       </c>
@@ -10610,7 +10628,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
         <v>473</v>
       </c>
@@ -10716,7 +10734,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
         <v>477</v>
       </c>
@@ -10822,7 +10840,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
         <v>480</v>
       </c>
@@ -10928,7 +10946,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
         <v>483</v>
       </c>
@@ -11037,6 +11055,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AL85">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI84">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T13:48:36+00:00</t>
+    <t>2025-05-23T10:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-location-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T10:50:09+00:00</t>
+    <t>2025-05-23T12:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
